--- a/backend/data/financials_by_company/002202.SZ.xlsx
+++ b/backend/data/financials_by_company/002202.SZ.xlsx
@@ -4586,10 +4586,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100176</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100176</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
